--- a/data/carddata.xlsx
+++ b/data/carddata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/41daa6e63c067b49/ドキュメント/GitHub/aikatsu-encore/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="8_{E3202D65-6DB6-41BF-AB49-900941BE025D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85F41C1B-60AF-4397-8F44-1E9B99166286}"/>
+  <xr:revisionPtr revIDLastSave="112" documentId="8_{E3202D65-6DB6-41BF-AB49-900941BE025D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EFFE5C96-F764-471B-A66D-3FBAAA52E43F}"/>
   <bookViews>
     <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{23D23E19-BA23-4316-91CC-981E46D7F5F5}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="258">
   <si>
     <t>カード番号</t>
     <rPh sb="3" eb="5">
@@ -885,6 +885,201 @@
   </si>
   <si>
     <t>プロモーションカード</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>EP-003</t>
+  </si>
+  <si>
+    <t>EP-004</t>
+  </si>
+  <si>
+    <t>EP-005</t>
+  </si>
+  <si>
+    <t>EP-006</t>
+  </si>
+  <si>
+    <t>EP-007</t>
+  </si>
+  <si>
+    <t>EP-008</t>
+  </si>
+  <si>
+    <t>EP-009</t>
+  </si>
+  <si>
+    <t>EP-010</t>
+  </si>
+  <si>
+    <t>EP-011</t>
+  </si>
+  <si>
+    <t>EP-012</t>
+  </si>
+  <si>
+    <t>EP-013</t>
+  </si>
+  <si>
+    <t>EP-014</t>
+  </si>
+  <si>
+    <t>EP-015</t>
+  </si>
+  <si>
+    <t>EP-016</t>
+  </si>
+  <si>
+    <t>EP-017</t>
+  </si>
+  <si>
+    <t>EP-018</t>
+  </si>
+  <si>
+    <t>エメラルドコクーンワンピ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アイカツ！スタイル購入特典配布</t>
+    <rPh sb="9" eb="11">
+      <t>コウニュウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>トクテン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ハイフ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エメラルドアゲハミュール</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ピンクシフォンカチューシャ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ピンクリボンつきフリルシャツ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>パフュームハンド アイカツ！</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ピンクアーガイルカーデ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アイカツフォン アンコール</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ピンクプリーツスカート</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ガーリーローファー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アイカツフォンキャリー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ピンクリボンカチューシャ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スターライト学園ピンクジャージ</t>
+    <rPh sb="6" eb="8">
+      <t>ガクエン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スターライト学園ブルージャージ</t>
+    <rPh sb="6" eb="8">
+      <t>ガクエン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スターライト学園パープルジャージ</t>
+    <rPh sb="6" eb="8">
+      <t>ガクエン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アイカツ！おうえんスターライト セクシータイプver.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アイカツ！おうえんスターライト クールタイプver.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アイカツ！おうえんスターライト キュートタイプver.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スターライト学園オレンジジャージ</t>
+    <rPh sb="6" eb="8">
+      <t>ガクエン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アイカツ！おうえんスターライト ポップタイプver.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スターライト学園スニーカー</t>
+    <rPh sb="6" eb="8">
+      <t>ガクエン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アイカツ！おうえんスターライト キュート/クール/セクシー/ポップタイプver.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ブラックダイヤモンドジュエリーワンピ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アイカツ！オフィシャルストア購入特典</t>
+    <rPh sb="14" eb="16">
+      <t>コウニュウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>トクテン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ピンクの小花柄ワンピ</t>
+    <rPh sb="4" eb="7">
+      <t>コバナガラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>編み上げラベンダーブーツ</t>
+    <rPh sb="0" eb="1">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>キュート/クール/セクシー/ポップ</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1281,13 +1476,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E75D5F29-00D8-47B4-8C37-01D4FAB6DC5C}">
-  <dimension ref="A1:I92"/>
+  <dimension ref="A1:I108"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.875" customWidth="1"/>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="28.5" customWidth="1"/>
-    <col min="4" max="4" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.25" customWidth="1"/>
     <col min="5" max="5" width="5.5" customWidth="1"/>
     <col min="6" max="7" width="9" customWidth="1"/>
     <col min="8" max="8" width="23.25" bestFit="1" customWidth="1"/>
@@ -3595,28 +3790,28 @@
         <v>214</v>
       </c>
       <c r="B89" t="s">
-        <v>180</v>
+        <v>215</v>
       </c>
       <c r="C89" t="s">
-        <v>188</v>
+        <v>231</v>
       </c>
       <c r="D89" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E89">
-        <v>1450</v>
+        <v>900</v>
       </c>
       <c r="F89" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G89" t="s">
         <v>192</v>
       </c>
       <c r="H89" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="I89" t="s">
-        <v>184</v>
+        <v>232</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.4">
@@ -3624,28 +3819,28 @@
         <v>214</v>
       </c>
       <c r="B90" t="s">
-        <v>181</v>
+        <v>216</v>
       </c>
       <c r="C90" t="s">
-        <v>189</v>
+        <v>233</v>
       </c>
       <c r="D90" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E90">
-        <v>650</v>
+        <v>350</v>
       </c>
       <c r="F90" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G90" t="s">
         <v>194</v>
       </c>
       <c r="H90" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="I90" t="s">
-        <v>184</v>
+        <v>232</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.4">
@@ -3653,28 +3848,28 @@
         <v>214</v>
       </c>
       <c r="B91" t="s">
-        <v>182</v>
+        <v>217</v>
       </c>
       <c r="C91" t="s">
-        <v>190</v>
+        <v>234</v>
       </c>
       <c r="D91" t="s">
         <v>211</v>
       </c>
       <c r="E91">
-        <v>850</v>
+        <v>350</v>
       </c>
       <c r="F91" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G91" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H91" t="s">
         <v>197</v>
       </c>
       <c r="I91" t="s">
-        <v>185</v>
+        <v>232</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.4">
@@ -3682,10 +3877,10 @@
         <v>214</v>
       </c>
       <c r="B92" t="s">
-        <v>183</v>
+        <v>218</v>
       </c>
       <c r="C92" t="s">
-        <v>191</v>
+        <v>235</v>
       </c>
       <c r="D92" t="s">
         <v>211</v>
@@ -3697,12 +3892,476 @@
         <v>195</v>
       </c>
       <c r="G92" t="s">
+        <v>92</v>
+      </c>
+      <c r="H92" t="s">
+        <v>197</v>
+      </c>
+      <c r="I92" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A93" t="s">
+        <v>214</v>
+      </c>
+      <c r="B93" t="s">
+        <v>219</v>
+      </c>
+      <c r="C93" t="s">
+        <v>237</v>
+      </c>
+      <c r="D93" t="s">
+        <v>211</v>
+      </c>
+      <c r="E93">
+        <v>400</v>
+      </c>
+      <c r="F93" t="s">
+        <v>195</v>
+      </c>
+      <c r="G93" t="s">
+        <v>92</v>
+      </c>
+      <c r="H93" t="s">
+        <v>198</v>
+      </c>
+      <c r="I93" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A94" t="s">
+        <v>214</v>
+      </c>
+      <c r="B94" t="s">
+        <v>220</v>
+      </c>
+      <c r="C94" t="s">
+        <v>239</v>
+      </c>
+      <c r="D94" t="s">
+        <v>211</v>
+      </c>
+      <c r="E94">
+        <v>500</v>
+      </c>
+      <c r="F94" t="s">
+        <v>195</v>
+      </c>
+      <c r="G94" t="s">
+        <v>205</v>
+      </c>
+      <c r="H94" t="s">
+        <v>198</v>
+      </c>
+      <c r="I94" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A95" t="s">
+        <v>214</v>
+      </c>
+      <c r="B95" t="s">
+        <v>221</v>
+      </c>
+      <c r="C95" t="s">
+        <v>240</v>
+      </c>
+      <c r="D95" t="s">
+        <v>211</v>
+      </c>
+      <c r="E95">
+        <v>350</v>
+      </c>
+      <c r="F95" t="s">
+        <v>195</v>
+      </c>
+      <c r="G95" t="s">
         <v>194</v>
       </c>
-      <c r="H92" t="s">
-        <v>197</v>
-      </c>
-      <c r="I92" t="s">
+      <c r="H95" t="s">
+        <v>198</v>
+      </c>
+      <c r="I95" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A96" t="s">
+        <v>214</v>
+      </c>
+      <c r="B96" t="s">
+        <v>222</v>
+      </c>
+      <c r="C96" t="s">
+        <v>242</v>
+      </c>
+      <c r="D96" t="s">
+        <v>211</v>
+      </c>
+      <c r="E96">
+        <v>350</v>
+      </c>
+      <c r="F96" t="s">
+        <v>195</v>
+      </c>
+      <c r="G96" t="s">
+        <v>193</v>
+      </c>
+      <c r="H96" t="s">
+        <v>197</v>
+      </c>
+      <c r="I96" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A97" t="s">
+        <v>214</v>
+      </c>
+      <c r="B97" t="s">
+        <v>223</v>
+      </c>
+      <c r="C97" t="s">
+        <v>243</v>
+      </c>
+      <c r="D97" t="s">
+        <v>211</v>
+      </c>
+      <c r="E97">
+        <v>850</v>
+      </c>
+      <c r="F97" t="s">
+        <v>195</v>
+      </c>
+      <c r="G97" t="s">
+        <v>192</v>
+      </c>
+      <c r="H97" t="s">
+        <v>197</v>
+      </c>
+      <c r="I97" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A98" t="s">
+        <v>214</v>
+      </c>
+      <c r="B98" t="s">
+        <v>224</v>
+      </c>
+      <c r="C98" t="s">
+        <v>244</v>
+      </c>
+      <c r="D98" t="s">
+        <v>211</v>
+      </c>
+      <c r="E98">
+        <v>850</v>
+      </c>
+      <c r="F98" t="s">
+        <v>203</v>
+      </c>
+      <c r="G98" t="s">
+        <v>192</v>
+      </c>
+      <c r="H98" t="s">
+        <v>197</v>
+      </c>
+      <c r="I98" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A99" t="s">
+        <v>214</v>
+      </c>
+      <c r="B99" t="s">
+        <v>225</v>
+      </c>
+      <c r="C99" t="s">
+        <v>245</v>
+      </c>
+      <c r="D99" t="s">
+        <v>211</v>
+      </c>
+      <c r="E99">
+        <v>850</v>
+      </c>
+      <c r="F99" t="s">
+        <v>196</v>
+      </c>
+      <c r="G99" t="s">
+        <v>192</v>
+      </c>
+      <c r="H99" t="s">
+        <v>197</v>
+      </c>
+      <c r="I99" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A100" t="s">
+        <v>214</v>
+      </c>
+      <c r="B100" t="s">
+        <v>226</v>
+      </c>
+      <c r="C100" t="s">
+        <v>249</v>
+      </c>
+      <c r="D100" t="s">
+        <v>211</v>
+      </c>
+      <c r="E100">
+        <v>850</v>
+      </c>
+      <c r="F100" t="s">
+        <v>204</v>
+      </c>
+      <c r="G100" t="s">
+        <v>192</v>
+      </c>
+      <c r="H100" t="s">
+        <v>197</v>
+      </c>
+      <c r="I100" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A101" t="s">
+        <v>214</v>
+      </c>
+      <c r="B101" t="s">
+        <v>227</v>
+      </c>
+      <c r="C101" t="s">
+        <v>251</v>
+      </c>
+      <c r="D101" t="s">
+        <v>211</v>
+      </c>
+      <c r="E101">
+        <v>400</v>
+      </c>
+      <c r="F101" t="s">
+        <v>257</v>
+      </c>
+      <c r="G101" t="s">
+        <v>194</v>
+      </c>
+      <c r="H101" t="s">
+        <v>197</v>
+      </c>
+      <c r="I101" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A102" t="s">
+        <v>214</v>
+      </c>
+      <c r="B102" t="s">
+        <v>228</v>
+      </c>
+      <c r="C102" t="s">
+        <v>253</v>
+      </c>
+      <c r="D102" t="s">
+        <v>211</v>
+      </c>
+      <c r="E102">
+        <v>850</v>
+      </c>
+      <c r="F102" t="s">
+        <v>196</v>
+      </c>
+      <c r="G102" t="s">
+        <v>192</v>
+      </c>
+      <c r="H102" t="s">
+        <v>197</v>
+      </c>
+      <c r="I102" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A103" t="s">
+        <v>214</v>
+      </c>
+      <c r="B103" t="s">
+        <v>229</v>
+      </c>
+      <c r="C103" t="s">
+        <v>255</v>
+      </c>
+      <c r="D103" t="s">
+        <v>211</v>
+      </c>
+      <c r="E103">
+        <v>900</v>
+      </c>
+      <c r="F103" t="s">
+        <v>195</v>
+      </c>
+      <c r="G103" t="s">
+        <v>192</v>
+      </c>
+      <c r="H103" t="s">
+        <v>198</v>
+      </c>
+      <c r="I103" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A104" t="s">
+        <v>214</v>
+      </c>
+      <c r="B104" t="s">
+        <v>230</v>
+      </c>
+      <c r="C104" t="s">
+        <v>256</v>
+      </c>
+      <c r="D104" t="s">
+        <v>211</v>
+      </c>
+      <c r="E104">
+        <v>350</v>
+      </c>
+      <c r="F104" t="s">
+        <v>195</v>
+      </c>
+      <c r="G104" t="s">
+        <v>194</v>
+      </c>
+      <c r="H104" t="s">
+        <v>198</v>
+      </c>
+      <c r="I104" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A105" t="s">
+        <v>214</v>
+      </c>
+      <c r="B105" t="s">
+        <v>180</v>
+      </c>
+      <c r="C105" t="s">
+        <v>188</v>
+      </c>
+      <c r="D105" t="s">
+        <v>210</v>
+      </c>
+      <c r="E105">
+        <v>1450</v>
+      </c>
+      <c r="F105" t="s">
+        <v>195</v>
+      </c>
+      <c r="G105" t="s">
+        <v>192</v>
+      </c>
+      <c r="H105" t="s">
+        <v>197</v>
+      </c>
+      <c r="I105" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A106" t="s">
+        <v>214</v>
+      </c>
+      <c r="B106" t="s">
+        <v>181</v>
+      </c>
+      <c r="C106" t="s">
+        <v>189</v>
+      </c>
+      <c r="D106" t="s">
+        <v>210</v>
+      </c>
+      <c r="E106">
+        <v>650</v>
+      </c>
+      <c r="F106" t="s">
+        <v>195</v>
+      </c>
+      <c r="G106" t="s">
+        <v>194</v>
+      </c>
+      <c r="H106" t="s">
+        <v>197</v>
+      </c>
+      <c r="I106" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A107" t="s">
+        <v>214</v>
+      </c>
+      <c r="B107" t="s">
+        <v>182</v>
+      </c>
+      <c r="C107" t="s">
+        <v>190</v>
+      </c>
+      <c r="D107" t="s">
+        <v>211</v>
+      </c>
+      <c r="E107">
+        <v>850</v>
+      </c>
+      <c r="F107" t="s">
+        <v>195</v>
+      </c>
+      <c r="G107" t="s">
+        <v>192</v>
+      </c>
+      <c r="H107" t="s">
+        <v>197</v>
+      </c>
+      <c r="I107" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A108" t="s">
+        <v>214</v>
+      </c>
+      <c r="B108" t="s">
+        <v>183</v>
+      </c>
+      <c r="C108" t="s">
+        <v>191</v>
+      </c>
+      <c r="D108" t="s">
+        <v>211</v>
+      </c>
+      <c r="E108">
+        <v>400</v>
+      </c>
+      <c r="F108" t="s">
+        <v>195</v>
+      </c>
+      <c r="G108" t="s">
+        <v>194</v>
+      </c>
+      <c r="H108" t="s">
+        <v>197</v>
+      </c>
+      <c r="I108" t="s">
         <v>185</v>
       </c>
     </row>

--- a/data/carddata.xlsx
+++ b/data/carddata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/41daa6e63c067b49/ドキュメント/GitHub/aikatsu-encore/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="112" documentId="8_{E3202D65-6DB6-41BF-AB49-900941BE025D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EFFE5C96-F764-471B-A66D-3FBAAA52E43F}"/>
+  <xr:revisionPtr revIDLastSave="194" documentId="8_{E3202D65-6DB6-41BF-AB49-900941BE025D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C11F89D7-48EA-482D-94A9-4E1FACEF438F}"/>
   <bookViews>
     <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{23D23E19-BA23-4316-91CC-981E46D7F5F5}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="290">
   <si>
     <t>カード番号</t>
     <rPh sb="3" eb="5">
@@ -1080,6 +1080,136 @@
   </si>
   <si>
     <t>キュート/クール/セクシー/ポップ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コーデ名</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>オーロラキス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アイスブルー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ドリーミー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>チャーミーリボン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クリアネスイエロー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ピンクステージ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>レモンラベンダー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ピンクブロッサム</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>天の川コズミック</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ブラック</t>
+  </si>
+  <si>
+    <t>ブルーステージ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ブラックストライプ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ネイビーブロッサム</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>レジェンダリールージュ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アゲハレッド</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>パープルジュエリー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アゲハロゴ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>パープルステージ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プッチがら</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>セクシーロゴ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>パープルブロッサム</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サンシャインスター</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サンライズスター</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サンセットスター</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>イエローブロッサム</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スターライト学園制服</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エンブレムつきセーラー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ピンクの小花柄</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ピンクアーガイル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エメラルドコクーン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スターライト学園</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1476,19 +1606,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E75D5F29-00D8-47B4-8C37-01D4FAB6DC5C}">
-  <dimension ref="A1:I108"/>
+  <dimension ref="A1:J108"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="12.875" customWidth="1"/>
-    <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5" customWidth="1"/>
-    <col min="4" max="4" width="11.25" customWidth="1"/>
-    <col min="5" max="5" width="5.5" customWidth="1"/>
-    <col min="6" max="7" width="9" customWidth="1"/>
-    <col min="8" max="8" width="23.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="47.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="32.625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.25" customWidth="1"/>
+    <col min="9" max="9" width="73.375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:10" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>212</v>
       </c>
@@ -1516,8 +1649,11 @@
       <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="J1" s="1" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>213</v>
       </c>
@@ -1542,8 +1678,11 @@
       <c r="H2" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="J2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>213</v>
       </c>
@@ -1568,8 +1707,11 @@
       <c r="H3" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="J3" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>213</v>
       </c>
@@ -1594,8 +1736,11 @@
       <c r="H4" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="J4" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>213</v>
       </c>
@@ -1620,8 +1765,11 @@
       <c r="H5" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="J5" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>213</v>
       </c>
@@ -1646,8 +1794,11 @@
       <c r="H6" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="J6" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>213</v>
       </c>
@@ -1672,8 +1823,11 @@
       <c r="H7" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="J7" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>213</v>
       </c>
@@ -1698,8 +1852,11 @@
       <c r="H8" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="J8" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>213</v>
       </c>
@@ -1724,8 +1881,11 @@
       <c r="H9" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="J9" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>213</v>
       </c>
@@ -1751,7 +1911,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>213</v>
       </c>
@@ -1776,8 +1936,11 @@
       <c r="H11" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="J11" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>213</v>
       </c>
@@ -1802,8 +1965,11 @@
       <c r="H12" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="J12" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>213</v>
       </c>
@@ -1828,8 +1994,11 @@
       <c r="H13" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="J13" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>213</v>
       </c>
@@ -1854,8 +2023,11 @@
       <c r="H14" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="J14" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>213</v>
       </c>
@@ -1880,8 +2052,11 @@
       <c r="H15" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="J15" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>213</v>
       </c>
@@ -1906,8 +2081,11 @@
       <c r="H16" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="J16" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>213</v>
       </c>
@@ -1932,8 +2110,11 @@
       <c r="H17" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="J17" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
         <v>213</v>
       </c>
@@ -1958,8 +2139,11 @@
       <c r="H18" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="J18" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
         <v>213</v>
       </c>
@@ -1984,8 +2168,11 @@
       <c r="H19" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="J19" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
         <v>213</v>
       </c>
@@ -2010,8 +2197,11 @@
       <c r="H20" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="J20" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
         <v>213</v>
       </c>
@@ -2036,8 +2226,11 @@
       <c r="H21" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="J21" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
         <v>213</v>
       </c>
@@ -2062,8 +2255,11 @@
       <c r="H22" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="J22" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
         <v>213</v>
       </c>
@@ -2088,8 +2284,11 @@
       <c r="H23" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="J23" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
         <v>213</v>
       </c>
@@ -2114,8 +2313,11 @@
       <c r="H24" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="J24" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
         <v>213</v>
       </c>
@@ -2140,8 +2342,11 @@
       <c r="H25" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="J25" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
         <v>213</v>
       </c>
@@ -2166,8 +2371,11 @@
       <c r="H26" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="J26" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
         <v>213</v>
       </c>
@@ -2192,8 +2400,11 @@
       <c r="H27" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="J27" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
         <v>213</v>
       </c>
@@ -2218,8 +2429,11 @@
       <c r="H28" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="J28" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
         <v>213</v>
       </c>
@@ -2244,8 +2458,11 @@
       <c r="H29" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="J29" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
         <v>213</v>
       </c>
@@ -2270,8 +2487,11 @@
       <c r="H30" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="J30" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
         <v>213</v>
       </c>
@@ -2297,7 +2517,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
         <v>213</v>
       </c>
@@ -2323,7 +2543,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
         <v>213</v>
       </c>
@@ -2349,7 +2569,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
         <v>213</v>
       </c>
@@ -2374,8 +2594,11 @@
       <c r="H34" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="J34" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
         <v>213</v>
       </c>
@@ -2400,8 +2623,11 @@
       <c r="H35" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="J35" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
         <v>213</v>
       </c>
@@ -2426,8 +2652,11 @@
       <c r="H36" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="J36" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
         <v>213</v>
       </c>
@@ -2452,8 +2681,11 @@
       <c r="H37" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="J37" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
         <v>213</v>
       </c>
@@ -2479,7 +2711,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
         <v>213</v>
       </c>
@@ -2504,8 +2736,11 @@
       <c r="H39" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="J39" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
         <v>213</v>
       </c>
@@ -2530,8 +2765,11 @@
       <c r="H40" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="J40" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
         <v>213</v>
       </c>
@@ -2556,8 +2794,11 @@
       <c r="H41" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="J41" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
         <v>213</v>
       </c>
@@ -2582,8 +2823,11 @@
       <c r="H42" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="J42" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
         <v>213</v>
       </c>
@@ -2608,8 +2852,11 @@
       <c r="H43" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="J43" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
         <v>213</v>
       </c>
@@ -2634,8 +2881,11 @@
       <c r="H44" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="J44" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
         <v>213</v>
       </c>
@@ -2660,8 +2910,11 @@
       <c r="H45" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="J45" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
         <v>213</v>
       </c>
@@ -2686,8 +2939,11 @@
       <c r="H46" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="J46" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
         <v>213</v>
       </c>
@@ -2712,8 +2968,11 @@
       <c r="H47" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="J47" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
         <v>213</v>
       </c>
@@ -2738,8 +2997,11 @@
       <c r="H48" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="J48" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
         <v>213</v>
       </c>
@@ -2764,8 +3026,11 @@
       <c r="H49" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="J49" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A50" t="s">
         <v>213</v>
       </c>
@@ -2790,8 +3055,11 @@
       <c r="H50" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="J50" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
         <v>213</v>
       </c>
@@ -2817,7 +3085,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
         <v>213</v>
       </c>
@@ -2842,8 +3110,11 @@
       <c r="H52" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="J52" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
         <v>213</v>
       </c>
@@ -2868,8 +3139,11 @@
       <c r="H53" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="J53" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A54" t="s">
         <v>213</v>
       </c>
@@ -2894,8 +3168,11 @@
       <c r="H54" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="J54" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
         <v>213</v>
       </c>
@@ -2920,8 +3197,11 @@
       <c r="H55" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="J55" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
         <v>213</v>
       </c>
@@ -2946,8 +3226,11 @@
       <c r="H56" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="J56" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
         <v>213</v>
       </c>
@@ -2972,8 +3255,11 @@
       <c r="H57" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="J57" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
         <v>213</v>
       </c>
@@ -2998,8 +3284,11 @@
       <c r="H58" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="J58" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
         <v>213</v>
       </c>
@@ -3024,8 +3313,11 @@
       <c r="H59" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="J59" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A60" t="s">
         <v>213</v>
       </c>
@@ -3050,8 +3342,11 @@
       <c r="H60" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="J60" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
         <v>213</v>
       </c>
@@ -3076,8 +3371,11 @@
       <c r="H61" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="J61" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
         <v>213</v>
       </c>
@@ -3102,8 +3400,11 @@
       <c r="H62" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="J62" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
         <v>213</v>
       </c>
@@ -3128,8 +3429,11 @@
       <c r="H63" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="J63" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A64" t="s">
         <v>213</v>
       </c>
@@ -3154,8 +3458,11 @@
       <c r="H64" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="J64" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A65" t="s">
         <v>213</v>
       </c>
@@ -3180,8 +3487,11 @@
       <c r="H65" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="J65" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A66" t="s">
         <v>213</v>
       </c>
@@ -3206,8 +3516,11 @@
       <c r="H66" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="J66" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A67" t="s">
         <v>213</v>
       </c>
@@ -3232,8 +3545,11 @@
       <c r="H67" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="J67" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A68" t="s">
         <v>213</v>
       </c>
@@ -3258,8 +3574,11 @@
       <c r="H68" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="J68" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A69" t="s">
         <v>213</v>
       </c>
@@ -3284,8 +3603,11 @@
       <c r="H69" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="J69" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A70" t="s">
         <v>213</v>
       </c>
@@ -3310,8 +3632,11 @@
       <c r="H70" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="J70" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A71" t="s">
         <v>213</v>
       </c>
@@ -3336,8 +3661,11 @@
       <c r="H71" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="J71" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A72" t="s">
         <v>213</v>
       </c>
@@ -3362,8 +3690,11 @@
       <c r="H72" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="J72" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A73" t="s">
         <v>213</v>
       </c>
@@ -3388,8 +3719,11 @@
       <c r="H73" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="J73" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A74" t="s">
         <v>213</v>
       </c>
@@ -3414,8 +3748,11 @@
       <c r="H74" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="J74" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A75" t="s">
         <v>213</v>
       </c>
@@ -3440,8 +3777,11 @@
       <c r="H75" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="J75" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A76" t="s">
         <v>213</v>
       </c>
@@ -3466,8 +3806,11 @@
       <c r="H76" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="J76" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A77" t="s">
         <v>213</v>
       </c>
@@ -3492,8 +3835,11 @@
       <c r="H77" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="J77" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A78" t="s">
         <v>213</v>
       </c>
@@ -3518,8 +3864,11 @@
       <c r="H78" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="J78" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A79" t="s">
         <v>213</v>
       </c>
@@ -3544,8 +3893,11 @@
       <c r="H79" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="J79" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A80" t="s">
         <v>213</v>
       </c>
@@ -3570,8 +3922,11 @@
       <c r="H80" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="J80" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A81" t="s">
         <v>213</v>
       </c>
@@ -3596,8 +3951,11 @@
       <c r="H81" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="J81" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A82" t="s">
         <v>213</v>
       </c>
@@ -3622,8 +3980,11 @@
       <c r="H82" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="J82" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A83" t="s">
         <v>213</v>
       </c>
@@ -3648,8 +4009,11 @@
       <c r="H83" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="J83" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A84" t="s">
         <v>213</v>
       </c>
@@ -3674,8 +4038,11 @@
       <c r="H84" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="J84" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A85" t="s">
         <v>213</v>
       </c>
@@ -3700,8 +4067,11 @@
       <c r="H85" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="J85" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A86" t="s">
         <v>213</v>
       </c>
@@ -3726,8 +4096,11 @@
       <c r="H86" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="J86" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A87" t="s">
         <v>214</v>
       </c>
@@ -3756,7 +4129,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A88" t="s">
         <v>214</v>
       </c>
@@ -3785,7 +4158,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A89" t="s">
         <v>214</v>
       </c>
@@ -3813,8 +4186,11 @@
       <c r="I89" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="J89" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A90" t="s">
         <v>214</v>
       </c>
@@ -3842,8 +4218,11 @@
       <c r="I90" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="J90" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A91" t="s">
         <v>214</v>
       </c>
@@ -3871,8 +4250,11 @@
       <c r="I91" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="J91" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A92" t="s">
         <v>214</v>
       </c>
@@ -3901,7 +4283,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A93" t="s">
         <v>214</v>
       </c>
@@ -3929,8 +4311,11 @@
       <c r="I93" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="J93" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A94" t="s">
         <v>214</v>
       </c>
@@ -3958,8 +4343,11 @@
       <c r="I94" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="J94" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A95" t="s">
         <v>214</v>
       </c>
@@ -3987,8 +4375,11 @@
       <c r="I95" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="J95" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A96" t="s">
         <v>214</v>
       </c>
@@ -4016,8 +4407,11 @@
       <c r="I96" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="J96" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A97" t="s">
         <v>214</v>
       </c>
@@ -4045,8 +4439,11 @@
       <c r="I97" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="J97" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A98" t="s">
         <v>214</v>
       </c>
@@ -4074,8 +4471,11 @@
       <c r="I98" t="s">
         <v>247</v>
       </c>
-    </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="J98" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A99" t="s">
         <v>214</v>
       </c>
@@ -4103,8 +4503,11 @@
       <c r="I99" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="J99" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A100" t="s">
         <v>214</v>
       </c>
@@ -4132,8 +4535,11 @@
       <c r="I100" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="J100" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A101" t="s">
         <v>214</v>
       </c>
@@ -4161,8 +4567,11 @@
       <c r="I101" t="s">
         <v>252</v>
       </c>
-    </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="J101" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A102" t="s">
         <v>214</v>
       </c>
@@ -4191,7 +4600,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A103" t="s">
         <v>214</v>
       </c>
@@ -4219,8 +4628,11 @@
       <c r="I103" t="s">
         <v>254</v>
       </c>
-    </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="J103" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A104" t="s">
         <v>214</v>
       </c>
@@ -4248,8 +4660,11 @@
       <c r="I104" t="s">
         <v>254</v>
       </c>
-    </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="J104" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A105" t="s">
         <v>214</v>
       </c>
@@ -4277,8 +4692,11 @@
       <c r="I105" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="J105" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A106" t="s">
         <v>214</v>
       </c>
@@ -4306,8 +4724,11 @@
       <c r="I106" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="J106" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A107" t="s">
         <v>214</v>
       </c>
@@ -4335,8 +4756,11 @@
       <c r="I107" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="J107" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A108" t="s">
         <v>214</v>
       </c>
@@ -4363,6 +4787,9 @@
       </c>
       <c r="I108" t="s">
         <v>185</v>
+      </c>
+      <c r="J108" t="s">
+        <v>285</v>
       </c>
     </row>
   </sheetData>

--- a/data/carddata.xlsx
+++ b/data/carddata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/41daa6e63c067b49/ドキュメント/GitHub/aikatsu-encore/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="194" documentId="8_{E3202D65-6DB6-41BF-AB49-900941BE025D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C11F89D7-48EA-482D-94A9-4E1FACEF438F}"/>
+  <xr:revisionPtr revIDLastSave="293" documentId="8_{E3202D65-6DB6-41BF-AB49-900941BE025D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{645F5CF7-8266-4A2F-9243-CF71511D916D}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{23D23E19-BA23-4316-91CC-981E46D7F5F5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{23D23E19-BA23-4316-91CC-981E46D7F5F5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1020" uniqueCount="317">
   <si>
     <t>カード番号</t>
     <rPh sb="3" eb="5">
@@ -165,9 +165,6 @@
   </si>
   <si>
     <t>E1-29</t>
-  </si>
-  <si>
-    <t>E1-30</t>
   </si>
   <si>
     <t>E1-31</t>
@@ -1210,6 +1207,109 @@
   </si>
   <si>
     <t>スターライト学園</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>EP-031</t>
+  </si>
+  <si>
+    <t>EP-032</t>
+  </si>
+  <si>
+    <t>EP-033</t>
+  </si>
+  <si>
+    <t>EP-034</t>
+  </si>
+  <si>
+    <t>EP-035</t>
+  </si>
+  <si>
+    <t>EP-036</t>
+  </si>
+  <si>
+    <t>ガーリーデビルスカート</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ガーリーデビルトップス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ガーリーデビルパンプス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>モンスターキャットトップス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>モンスターキャットスカート</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>モンスターキャットファーブーツ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データカードダス アイカツ！アンコール アイカツ！キャンペーン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ガーリーデビル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>モンスターキャット</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>E1-01★</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>E1-02★</t>
+  </si>
+  <si>
+    <t>E1-03★</t>
+  </si>
+  <si>
+    <t>E1-04★</t>
+  </si>
+  <si>
+    <t>E1-30</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>E1-30★</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>E1-31★</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>E1-32★</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>E1-33★</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>E1-34★</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>E1-35★</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>E1-36★</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>E1-50★</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1287,6 +1387,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1606,7 +1710,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E75D5F29-00D8-47B4-8C37-01D4FAB6DC5C}">
-  <dimension ref="A1:J108"/>
+  <dimension ref="A1:J126"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="21.25" bestFit="1" customWidth="1"/>
@@ -1623,7 +1727,7 @@
   <sheetData>
     <row r="1" spans="1:10" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -1632,10 +1736,10 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>2</v>
@@ -1650,2971 +1754,2917 @@
         <v>5</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B2" t="s">
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E2">
         <v>1100</v>
       </c>
       <c r="F2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B3" t="s">
         <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E3">
         <v>1000</v>
       </c>
       <c r="F3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B4" t="s">
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E4">
         <v>950</v>
       </c>
       <c r="F4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B5" t="s">
         <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E5">
         <v>600</v>
       </c>
       <c r="F5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J5" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>304</v>
       </c>
       <c r="C6" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="D6" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E6">
-        <v>600</v>
+        <v>1100</v>
       </c>
       <c r="F6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J6" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>305</v>
       </c>
       <c r="C7" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D7" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E7">
-        <v>750</v>
+        <v>1000</v>
       </c>
       <c r="F7" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H7" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J7" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>306</v>
       </c>
       <c r="C8" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D8" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E8">
-        <v>750</v>
+        <v>950</v>
       </c>
       <c r="F8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J8" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>307</v>
       </c>
       <c r="C9" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D9" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E9">
-        <v>450</v>
+        <v>600</v>
       </c>
       <c r="F9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H9" t="s">
         <v>197</v>
       </c>
       <c r="J9" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C10" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D10" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E10">
-        <v>1450</v>
+        <v>600</v>
       </c>
       <c r="F10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G10" t="s">
-        <v>192</v>
+        <v>91</v>
       </c>
       <c r="H10" t="s">
-        <v>198</v>
+        <v>197</v>
+      </c>
+      <c r="J10" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C11" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D11" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E11">
         <v>750</v>
       </c>
       <c r="F11" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G11" t="s">
-        <v>92</v>
+        <v>204</v>
       </c>
       <c r="H11" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="J11" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B12" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C12" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D12" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E12">
-        <v>650</v>
+        <v>750</v>
       </c>
       <c r="F12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G12" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="H12" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="J12" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B13" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D13" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E13">
-        <v>700</v>
+        <v>450</v>
       </c>
       <c r="F13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G13" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H13" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="J13" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B14" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C14" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D14" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E14">
-        <v>650</v>
+        <v>1450</v>
       </c>
       <c r="F14" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G14" t="s">
-        <v>92</v>
+        <v>191</v>
       </c>
       <c r="H14" t="s">
-        <v>202</v>
-      </c>
-      <c r="J14" t="s">
-        <v>262</v>
+        <v>197</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B15" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C15" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="D15" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E15">
-        <v>700</v>
+        <v>750</v>
       </c>
       <c r="F15" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G15" t="s">
-        <v>205</v>
+        <v>91</v>
       </c>
       <c r="H15" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="J15" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B16" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C16" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D16" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E16">
-        <v>750</v>
+        <v>650</v>
       </c>
       <c r="F16" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G16" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="H16" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="J16" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B17" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C17" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D17" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E17">
-        <v>450</v>
+        <v>700</v>
       </c>
       <c r="F17" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G17" t="s">
         <v>193</v>
       </c>
       <c r="H17" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="J17" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B18" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C18" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="D18" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E18">
-        <v>700</v>
+        <v>650</v>
       </c>
       <c r="F18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G18" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H18" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="J18" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B19" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C19" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D19" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E19">
-        <v>750</v>
+        <v>700</v>
       </c>
       <c r="F19" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G19" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H19" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="J19" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B20" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C20" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="D20" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E20">
-        <v>650</v>
+        <v>750</v>
       </c>
       <c r="F20" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G20" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H20" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="J20" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B21" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C21" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="D21" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E21">
         <v>450</v>
       </c>
       <c r="F21" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G21" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H21" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="J21" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C22" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D22" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E22">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="F22" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G22" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H22" t="s">
         <v>197</v>
       </c>
       <c r="J22" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B23" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C23" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="D23" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E23">
-        <v>400</v>
+        <v>750</v>
       </c>
       <c r="F23" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G23" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H23" t="s">
         <v>197</v>
       </c>
       <c r="J23" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B24" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C24" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="D24" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E24">
-        <v>350</v>
+        <v>650</v>
       </c>
       <c r="F24" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G24" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H24" t="s">
         <v>197</v>
       </c>
       <c r="J24" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B25" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C25" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D25" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E25">
         <v>450</v>
       </c>
       <c r="F25" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G25" t="s">
-        <v>92</v>
+        <v>192</v>
       </c>
       <c r="H25" t="s">
         <v>197</v>
       </c>
       <c r="J25" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B26" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C26" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="D26" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E26">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="F26" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G26" t="s">
-        <v>205</v>
+        <v>91</v>
       </c>
       <c r="H26" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J26" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B27" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C27" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="D27" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E27">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="F27" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G27" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="H27" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J27" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B28" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C28" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D28" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E28">
-        <v>500</v>
+        <v>350</v>
       </c>
       <c r="F28" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G28" t="s">
-        <v>92</v>
+        <v>193</v>
       </c>
       <c r="H28" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J28" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B29" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C29" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="D29" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E29">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="F29" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G29" t="s">
-        <v>205</v>
+        <v>91</v>
       </c>
       <c r="H29" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J29" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B30" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C30" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D30" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E30">
-        <v>350</v>
+        <v>450</v>
       </c>
       <c r="F30" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G30" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="H30" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J30" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B31" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C31" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D31" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E31">
-        <v>3650</v>
+        <v>350</v>
       </c>
       <c r="F31" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G31" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="H31" t="s">
-        <v>201</v>
+        <v>196</v>
+      </c>
+      <c r="J31" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B32" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C32" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="D32" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E32">
-        <v>3650</v>
+        <v>500</v>
       </c>
       <c r="F32" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G32" t="s">
-        <v>206</v>
+        <v>91</v>
       </c>
       <c r="H32" t="s">
-        <v>202</v>
+        <v>196</v>
+      </c>
+      <c r="J32" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B33" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C33" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="D33" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E33">
-        <v>3650</v>
+        <v>400</v>
       </c>
       <c r="F33" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G33" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="H33" t="s">
-        <v>197</v>
+        <v>196</v>
+      </c>
+      <c r="J33" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B34" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C34" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D34" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E34">
-        <v>1100</v>
+        <v>350</v>
       </c>
       <c r="F34" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="G34" t="s">
-        <v>92</v>
+        <v>193</v>
       </c>
       <c r="H34" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="J34" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B35" t="s">
-        <v>39</v>
+        <v>308</v>
       </c>
       <c r="C35" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D35" t="s">
         <v>208</v>
       </c>
       <c r="E35">
-        <v>950</v>
+        <v>3650</v>
       </c>
       <c r="F35" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="G35" t="s">
         <v>205</v>
       </c>
       <c r="H35" t="s">
-        <v>199</v>
-      </c>
-      <c r="J35" t="s">
-        <v>267</v>
+        <v>200</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B36" t="s">
-        <v>40</v>
+        <v>309</v>
       </c>
       <c r="C36" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="D36" t="s">
         <v>208</v>
       </c>
       <c r="E36">
-        <v>1000</v>
+        <v>3650</v>
       </c>
       <c r="F36" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="G36" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="H36" t="s">
-        <v>199</v>
-      </c>
-      <c r="J36" t="s">
-        <v>267</v>
+        <v>200</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B37" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C37" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="D37" t="s">
         <v>208</v>
       </c>
       <c r="E37">
-        <v>600</v>
+        <v>3650</v>
       </c>
       <c r="F37" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="G37" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="H37" t="s">
-        <v>199</v>
-      </c>
-      <c r="J37" t="s">
-        <v>267</v>
+        <v>201</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B38" t="s">
-        <v>42</v>
+        <v>310</v>
       </c>
       <c r="C38" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D38" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E38">
-        <v>1450</v>
+        <v>3650</v>
       </c>
       <c r="F38" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="G38" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="H38" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B39" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="C39" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="D39" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E39">
-        <v>700</v>
+        <v>3650</v>
       </c>
       <c r="F39" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="G39" t="s">
-        <v>92</v>
+        <v>205</v>
       </c>
       <c r="H39" t="s">
-        <v>199</v>
-      </c>
-      <c r="J39" t="s">
-        <v>268</v>
+        <v>196</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B40" t="s">
-        <v>44</v>
+        <v>311</v>
       </c>
       <c r="C40" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="D40" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E40">
-        <v>750</v>
+        <v>3650</v>
       </c>
       <c r="F40" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="G40" t="s">
         <v>205</v>
       </c>
       <c r="H40" t="s">
-        <v>199</v>
-      </c>
-      <c r="J40" t="s">
-        <v>268</v>
+        <v>196</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B41" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C41" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="D41" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E41">
-        <v>650</v>
+        <v>1100</v>
       </c>
       <c r="F41" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G41" t="s">
-        <v>194</v>
+        <v>91</v>
       </c>
       <c r="H41" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="J41" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B42" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C42" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="D42" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E42">
-        <v>400</v>
+        <v>950</v>
       </c>
       <c r="F42" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G42" t="s">
-        <v>92</v>
+        <v>204</v>
       </c>
       <c r="H42" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J42" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B43" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C43" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="D43" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E43">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="F43" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G43" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="H43" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J43" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B44" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C44" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="D44" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E44">
-        <v>350</v>
+        <v>600</v>
       </c>
       <c r="F44" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G44" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H44" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J44" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B45" t="s">
-        <v>49</v>
+        <v>312</v>
       </c>
       <c r="C45" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="D45" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E45">
-        <v>400</v>
+        <v>1100</v>
       </c>
       <c r="F45" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G45" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H45" t="s">
-        <v>197</v>
-      </c>
-      <c r="J45" t="s">
-        <v>270</v>
+        <v>198</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B46" t="s">
-        <v>50</v>
+        <v>313</v>
       </c>
       <c r="C46" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="D46" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E46">
-        <v>450</v>
+        <v>950</v>
       </c>
       <c r="F46" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G46" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H46" t="s">
-        <v>197</v>
-      </c>
-      <c r="J46" t="s">
-        <v>270</v>
+        <v>198</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B47" t="s">
-        <v>51</v>
+        <v>314</v>
       </c>
       <c r="C47" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="D47" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E47">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="F47" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G47" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H47" t="s">
-        <v>197</v>
-      </c>
-      <c r="J47" t="s">
-        <v>270</v>
+        <v>198</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B48" t="s">
-        <v>52</v>
+        <v>315</v>
       </c>
       <c r="C48" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="D48" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E48">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="F48" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G48" t="s">
-        <v>92</v>
+        <v>192</v>
       </c>
       <c r="H48" t="s">
-        <v>197</v>
-      </c>
-      <c r="J48" t="s">
-        <v>271</v>
+        <v>198</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B49" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="C49" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="D49" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E49">
-        <v>500</v>
+        <v>1450</v>
       </c>
       <c r="F49" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G49" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="H49" t="s">
-        <v>197</v>
-      </c>
-      <c r="J49" t="s">
-        <v>271</v>
+        <v>198</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A50" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B50" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="C50" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="D50" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E50">
-        <v>350</v>
+        <v>700</v>
       </c>
       <c r="F50" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G50" t="s">
-        <v>194</v>
+        <v>91</v>
       </c>
       <c r="H50" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J50" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B51" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="C51" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="D51" t="s">
         <v>209</v>
       </c>
       <c r="E51">
-        <v>3650</v>
+        <v>750</v>
       </c>
       <c r="F51" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G51" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="H51" t="s">
-        <v>197</v>
+        <v>198</v>
+      </c>
+      <c r="J51" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B52" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="C52" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="D52" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E52">
-        <v>2000</v>
+        <v>650</v>
       </c>
       <c r="F52" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="G52" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H52" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J52" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B53" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C53" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="D53" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E53">
-        <v>1050</v>
+        <v>400</v>
       </c>
       <c r="F53" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="G53" t="s">
-        <v>194</v>
+        <v>91</v>
       </c>
       <c r="H53" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J53" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A54" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B54" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="C54" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="D54" t="s">
         <v>210</v>
       </c>
       <c r="E54">
-        <v>1450</v>
+        <v>500</v>
       </c>
       <c r="F54" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="G54" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="H54" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="J54" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B55" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="C55" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="D55" t="s">
         <v>210</v>
       </c>
       <c r="E55">
-        <v>650</v>
+        <v>350</v>
       </c>
       <c r="F55" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="G55" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H55" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="J55" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B56" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="C56" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="D56" t="s">
         <v>210</v>
       </c>
       <c r="E56">
-        <v>1450</v>
+        <v>400</v>
       </c>
       <c r="F56" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="G56" t="s">
-        <v>192</v>
+        <v>91</v>
       </c>
       <c r="H56" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="J56" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B57" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="C57" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="D57" t="s">
         <v>210</v>
       </c>
       <c r="E57">
-        <v>650</v>
+        <v>450</v>
       </c>
       <c r="F57" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="G57" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="H57" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="J57" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B58" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="C58" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="D58" t="s">
         <v>210</v>
       </c>
       <c r="E58">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="F58" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="G58" t="s">
-        <v>92</v>
+        <v>193</v>
       </c>
       <c r="H58" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="J58" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B59" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="C59" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="D59" t="s">
         <v>210</v>
       </c>
       <c r="E59">
-        <v>750</v>
+        <v>400</v>
       </c>
       <c r="F59" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="G59" t="s">
-        <v>205</v>
+        <v>91</v>
       </c>
       <c r="H59" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="J59" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A60" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B60" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="C60" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="D60" t="s">
         <v>210</v>
       </c>
       <c r="E60">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="F60" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="G60" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="H60" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J60" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B61" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="C61" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="D61" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E61">
-        <v>500</v>
+        <v>350</v>
       </c>
       <c r="F61" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="G61" t="s">
-        <v>92</v>
+        <v>193</v>
       </c>
       <c r="H61" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J61" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B62" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="C62" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="D62" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E62">
-        <v>350</v>
+        <v>3650</v>
       </c>
       <c r="F62" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="G62" t="s">
         <v>205</v>
       </c>
       <c r="H62" t="s">
-        <v>197</v>
-      </c>
-      <c r="J62" t="s">
-        <v>276</v>
+        <v>196</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B63" t="s">
-        <v>67</v>
+        <v>316</v>
       </c>
       <c r="C63" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="D63" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E63">
-        <v>400</v>
+        <v>3650</v>
       </c>
       <c r="F63" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="G63" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="H63" t="s">
-        <v>197</v>
-      </c>
-      <c r="J63" t="s">
-        <v>276</v>
+        <v>196</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A64" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B64" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="C64" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="D64" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E64">
-        <v>450</v>
+        <v>2000</v>
       </c>
       <c r="F64" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G64" t="s">
-        <v>92</v>
+        <v>191</v>
       </c>
       <c r="H64" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J64" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A65" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B65" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="C65" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="D65" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E65">
-        <v>450</v>
+        <v>1050</v>
       </c>
       <c r="F65" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G65" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="H65" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J65" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A66" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B66" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="C66" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="D66" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E66">
-        <v>400</v>
+        <v>1450</v>
       </c>
       <c r="F66" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G66" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="H66" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="J66" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A67" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B67" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="C67" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="D67" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E67">
-        <v>450</v>
+        <v>650</v>
       </c>
       <c r="F67" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G67" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="H67" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="J67" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A68" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B68" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="C68" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="D68" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E68">
-        <v>400</v>
+        <v>1450</v>
       </c>
       <c r="F68" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G68" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="H68" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="J68" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A69" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B69" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="C69" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="D69" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E69">
-        <v>500</v>
+        <v>650</v>
       </c>
       <c r="F69" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G69" t="s">
-        <v>92</v>
+        <v>193</v>
       </c>
       <c r="H69" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="J69" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A70" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B70" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="C70" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="D70" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E70">
-        <v>350</v>
+        <v>700</v>
       </c>
       <c r="F70" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G70" t="s">
-        <v>205</v>
+        <v>91</v>
       </c>
       <c r="H70" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="J70" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A71" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B71" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="C71" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="D71" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E71">
-        <v>400</v>
+        <v>750</v>
       </c>
       <c r="F71" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G71" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="H71" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="J71" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A72" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B72" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="C72" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="D72" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E72">
-        <v>1000</v>
+        <v>450</v>
       </c>
       <c r="F72" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="G72" t="s">
-        <v>92</v>
+        <v>193</v>
       </c>
       <c r="H72" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J72" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A73" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B73" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="C73" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="D73" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E73">
-        <v>1100</v>
+        <v>500</v>
       </c>
       <c r="F73" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="G73" t="s">
-        <v>205</v>
+        <v>91</v>
       </c>
       <c r="H73" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J73" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A74" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B74" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="C74" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="D74" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E74">
-        <v>950</v>
+        <v>350</v>
       </c>
       <c r="F74" t="s">
+        <v>195</v>
+      </c>
+      <c r="G74" t="s">
         <v>204</v>
       </c>
-      <c r="G74" t="s">
-        <v>194</v>
-      </c>
       <c r="H74" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J74" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A75" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B75" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="C75" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="D75" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E75">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="F75" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="G75" t="s">
         <v>193</v>
       </c>
       <c r="H75" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J75" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A76" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B76" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="C76" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="D76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E76">
-        <v>1100</v>
+        <v>450</v>
       </c>
       <c r="F76" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="G76" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H76" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J76" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A77" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B77" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="C77" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="D77" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E77">
-        <v>950</v>
+        <v>450</v>
       </c>
       <c r="F77" t="s">
+        <v>195</v>
+      </c>
+      <c r="G77" t="s">
         <v>204</v>
       </c>
-      <c r="G77" t="s">
-        <v>205</v>
-      </c>
       <c r="H77" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J77" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A78" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B78" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="C78" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="D78" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E78">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="F78" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="G78" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H78" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J78" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A79" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B79" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="C79" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="D79" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E79">
-        <v>600</v>
+        <v>450</v>
       </c>
       <c r="F79" t="s">
+        <v>195</v>
+      </c>
+      <c r="G79" t="s">
         <v>204</v>
       </c>
-      <c r="G79" t="s">
-        <v>193</v>
-      </c>
       <c r="H79" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J79" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A80" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B80" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="C80" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="D80" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E80">
-        <v>950</v>
+        <v>400</v>
       </c>
       <c r="F80" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="G80" t="s">
-        <v>92</v>
+        <v>193</v>
       </c>
       <c r="H80" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J80" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A81" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B81" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="C81" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="D81" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E81">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="F81" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="G81" t="s">
-        <v>205</v>
+        <v>91</v>
       </c>
       <c r="H81" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J81" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A82" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B82" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="C82" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="D82" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E82">
-        <v>1100</v>
+        <v>350</v>
       </c>
       <c r="F82" t="s">
+        <v>195</v>
+      </c>
+      <c r="G82" t="s">
         <v>204</v>
       </c>
-      <c r="G82" t="s">
-        <v>194</v>
-      </c>
       <c r="H82" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J82" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A83" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B83" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="C83" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="D83" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E83">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="F83" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="G83" t="s">
         <v>193</v>
       </c>
       <c r="H83" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J83" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A84" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B84" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="C84" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="D84" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E84">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="F84" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G84" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H84" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J84" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A85" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B85" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="C85" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="D85" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E85">
-        <v>350</v>
+        <v>1100</v>
       </c>
       <c r="F85" t="s">
+        <v>203</v>
+      </c>
+      <c r="G85" t="s">
         <v>204</v>
       </c>
-      <c r="G85" t="s">
-        <v>205</v>
-      </c>
       <c r="H85" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J85" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A86" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B86" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="C86" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="D86" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E86">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="F86" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G86" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H86" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J86" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A87" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B87" t="s">
-        <v>178</v>
+        <v>78</v>
       </c>
       <c r="C87" t="s">
-        <v>186</v>
+        <v>165</v>
       </c>
       <c r="D87" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E87">
-        <v>900</v>
+        <v>600</v>
       </c>
       <c r="F87" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="G87" t="s">
         <v>192</v>
       </c>
       <c r="H87" t="s">
-        <v>197</v>
-      </c>
-      <c r="I87" t="s">
-        <v>184</v>
+        <v>196</v>
+      </c>
+      <c r="J87" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A88" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B88" t="s">
-        <v>179</v>
+        <v>79</v>
       </c>
       <c r="C88" t="s">
-        <v>187</v>
+        <v>166</v>
       </c>
       <c r="D88" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E88">
-        <v>600</v>
+        <v>1100</v>
       </c>
       <c r="F88" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="G88" t="s">
-        <v>193</v>
+        <v>91</v>
       </c>
       <c r="H88" t="s">
-        <v>197</v>
-      </c>
-      <c r="I88" t="s">
-        <v>184</v>
+        <v>196</v>
+      </c>
+      <c r="J88" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A89" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B89" t="s">
-        <v>215</v>
+        <v>80</v>
       </c>
       <c r="C89" t="s">
-        <v>231</v>
+        <v>167</v>
       </c>
       <c r="D89" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E89">
-        <v>900</v>
+        <v>950</v>
       </c>
       <c r="F89" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="G89" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="H89" t="s">
-        <v>200</v>
-      </c>
-      <c r="I89" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="J89" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A90" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B90" t="s">
-        <v>216</v>
+        <v>81</v>
       </c>
       <c r="C90" t="s">
-        <v>233</v>
+        <v>168</v>
       </c>
       <c r="D90" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E90">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="F90" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="G90" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H90" t="s">
-        <v>200</v>
-      </c>
-      <c r="I90" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="J90" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A91" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B91" t="s">
-        <v>217</v>
+        <v>82</v>
       </c>
       <c r="C91" t="s">
-        <v>234</v>
+        <v>169</v>
       </c>
       <c r="D91" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E91">
-        <v>350</v>
+        <v>600</v>
       </c>
       <c r="F91" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="G91" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H91" t="s">
-        <v>197</v>
-      </c>
-      <c r="I91" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="J91" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A92" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B92" t="s">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="C92" t="s">
-        <v>235</v>
+        <v>170</v>
       </c>
       <c r="D92" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E92">
-        <v>400</v>
+        <v>950</v>
       </c>
       <c r="F92" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="G92" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H92" t="s">
-        <v>197</v>
-      </c>
-      <c r="I92" t="s">
-        <v>236</v>
+        <v>196</v>
+      </c>
+      <c r="J92" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A93" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B93" t="s">
-        <v>219</v>
+        <v>84</v>
       </c>
       <c r="C93" t="s">
-        <v>237</v>
+        <v>171</v>
       </c>
       <c r="D93" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E93">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="F93" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="G93" t="s">
-        <v>92</v>
+        <v>204</v>
       </c>
       <c r="H93" t="s">
-        <v>198</v>
-      </c>
-      <c r="I93" t="s">
-        <v>238</v>
+        <v>196</v>
       </c>
       <c r="J93" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A94" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B94" t="s">
-        <v>220</v>
+        <v>85</v>
       </c>
       <c r="C94" t="s">
-        <v>239</v>
+        <v>172</v>
       </c>
       <c r="D94" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E94">
-        <v>500</v>
+        <v>1100</v>
       </c>
       <c r="F94" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="G94" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="H94" t="s">
-        <v>198</v>
-      </c>
-      <c r="I94" t="s">
-        <v>238</v>
+        <v>196</v>
       </c>
       <c r="J94" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A95" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B95" t="s">
-        <v>221</v>
+        <v>86</v>
       </c>
       <c r="C95" t="s">
-        <v>240</v>
+        <v>173</v>
       </c>
       <c r="D95" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E95">
-        <v>350</v>
+        <v>600</v>
       </c>
       <c r="F95" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="G95" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H95" t="s">
-        <v>198</v>
-      </c>
-      <c r="I95" t="s">
-        <v>238</v>
+        <v>196</v>
       </c>
       <c r="J95" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A96" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B96" t="s">
-        <v>222</v>
+        <v>87</v>
       </c>
       <c r="C96" t="s">
-        <v>242</v>
+        <v>174</v>
       </c>
       <c r="D96" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E96">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="F96" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="G96" t="s">
-        <v>193</v>
+        <v>91</v>
       </c>
       <c r="H96" t="s">
-        <v>197</v>
-      </c>
-      <c r="I96" t="s">
-        <v>241</v>
+        <v>196</v>
       </c>
       <c r="J96" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A97" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B97" t="s">
-        <v>223</v>
+        <v>88</v>
       </c>
       <c r="C97" t="s">
-        <v>243</v>
+        <v>175</v>
       </c>
       <c r="D97" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E97">
-        <v>850</v>
+        <v>350</v>
       </c>
       <c r="F97" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="G97" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="H97" t="s">
-        <v>197</v>
-      </c>
-      <c r="I97" t="s">
-        <v>248</v>
+        <v>196</v>
       </c>
       <c r="J97" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A98" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B98" t="s">
-        <v>224</v>
+        <v>89</v>
       </c>
       <c r="C98" t="s">
-        <v>244</v>
+        <v>176</v>
       </c>
       <c r="D98" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E98">
-        <v>850</v>
+        <v>500</v>
       </c>
       <c r="F98" t="s">
         <v>203</v>
       </c>
       <c r="G98" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H98" t="s">
-        <v>197</v>
-      </c>
-      <c r="I98" t="s">
-        <v>247</v>
+        <v>196</v>
       </c>
       <c r="J98" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A99" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B99" t="s">
-        <v>225</v>
+        <v>177</v>
       </c>
       <c r="C99" t="s">
-        <v>245</v>
+        <v>185</v>
       </c>
       <c r="D99" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E99">
-        <v>850</v>
+        <v>900</v>
       </c>
       <c r="F99" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="G99" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H99" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I99" t="s">
-        <v>246</v>
-      </c>
-      <c r="J99" t="s">
-        <v>289</v>
+        <v>183</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A100" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B100" t="s">
-        <v>226</v>
+        <v>178</v>
       </c>
       <c r="C100" t="s">
-        <v>249</v>
+        <v>186</v>
       </c>
       <c r="D100" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E100">
-        <v>850</v>
+        <v>600</v>
       </c>
       <c r="F100" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="G100" t="s">
         <v>192</v>
       </c>
       <c r="H100" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I100" t="s">
-        <v>250</v>
-      </c>
-      <c r="J100" t="s">
-        <v>289</v>
+        <v>183</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A101" t="s">
+        <v>213</v>
+      </c>
+      <c r="B101" t="s">
         <v>214</v>
       </c>
-      <c r="B101" t="s">
-        <v>227</v>
-      </c>
       <c r="C101" t="s">
-        <v>251</v>
+        <v>230</v>
       </c>
       <c r="D101" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E101">
-        <v>400</v>
+        <v>900</v>
       </c>
       <c r="F101" t="s">
-        <v>257</v>
+        <v>195</v>
       </c>
       <c r="G101" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="H101" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="I101" t="s">
-        <v>252</v>
+        <v>231</v>
       </c>
       <c r="J101" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A102" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B102" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="C102" t="s">
-        <v>253</v>
+        <v>232</v>
       </c>
       <c r="D102" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E102">
-        <v>850</v>
+        <v>350</v>
       </c>
       <c r="F102" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G102" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H102" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="I102" t="s">
-        <v>254</v>
+        <v>231</v>
+      </c>
+      <c r="J102" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A103" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B103" t="s">
-        <v>229</v>
+        <v>216</v>
       </c>
       <c r="C103" t="s">
-        <v>255</v>
+        <v>233</v>
       </c>
       <c r="D103" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E103">
-        <v>900</v>
+        <v>350</v>
       </c>
       <c r="F103" t="s">
         <v>195</v>
@@ -4623,173 +4673,743 @@
         <v>192</v>
       </c>
       <c r="H103" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="I103" t="s">
-        <v>254</v>
+        <v>231</v>
       </c>
       <c r="J103" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A104" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B104" t="s">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="C104" t="s">
-        <v>256</v>
+        <v>234</v>
       </c>
       <c r="D104" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E104">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="F104" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G104" t="s">
-        <v>194</v>
+        <v>91</v>
       </c>
       <c r="H104" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="I104" t="s">
-        <v>254</v>
-      </c>
-      <c r="J104" t="s">
-        <v>286</v>
+        <v>235</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A105" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B105" t="s">
-        <v>180</v>
+        <v>218</v>
       </c>
       <c r="C105" t="s">
-        <v>188</v>
+        <v>236</v>
       </c>
       <c r="D105" t="s">
         <v>210</v>
       </c>
       <c r="E105">
-        <v>1450</v>
+        <v>400</v>
       </c>
       <c r="F105" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G105" t="s">
-        <v>192</v>
+        <v>91</v>
       </c>
       <c r="H105" t="s">
         <v>197</v>
       </c>
       <c r="I105" t="s">
-        <v>184</v>
+        <v>237</v>
       </c>
       <c r="J105" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A106" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B106" t="s">
-        <v>181</v>
+        <v>219</v>
       </c>
       <c r="C106" t="s">
-        <v>189</v>
+        <v>238</v>
       </c>
       <c r="D106" t="s">
         <v>210</v>
       </c>
       <c r="E106">
-        <v>650</v>
+        <v>500</v>
       </c>
       <c r="F106" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G106" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="H106" t="s">
         <v>197</v>
       </c>
       <c r="I106" t="s">
-        <v>184</v>
+        <v>237</v>
       </c>
       <c r="J106" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A107" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B107" t="s">
-        <v>182</v>
+        <v>220</v>
       </c>
       <c r="C107" t="s">
-        <v>190</v>
+        <v>239</v>
       </c>
       <c r="D107" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E107">
-        <v>850</v>
+        <v>350</v>
       </c>
       <c r="F107" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G107" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H107" t="s">
         <v>197</v>
       </c>
       <c r="I107" t="s">
-        <v>185</v>
+        <v>237</v>
       </c>
       <c r="J107" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A108" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B108" t="s">
+        <v>221</v>
+      </c>
+      <c r="C108" t="s">
+        <v>241</v>
+      </c>
+      <c r="D108" t="s">
+        <v>210</v>
+      </c>
+      <c r="E108">
+        <v>350</v>
+      </c>
+      <c r="F108" t="s">
+        <v>194</v>
+      </c>
+      <c r="G108" t="s">
+        <v>192</v>
+      </c>
+      <c r="H108" t="s">
+        <v>196</v>
+      </c>
+      <c r="I108" t="s">
+        <v>240</v>
+      </c>
+      <c r="J108" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A109" t="s">
+        <v>213</v>
+      </c>
+      <c r="B109" t="s">
+        <v>222</v>
+      </c>
+      <c r="C109" t="s">
+        <v>242</v>
+      </c>
+      <c r="D109" t="s">
+        <v>210</v>
+      </c>
+      <c r="E109">
+        <v>850</v>
+      </c>
+      <c r="F109" t="s">
+        <v>194</v>
+      </c>
+      <c r="G109" t="s">
+        <v>191</v>
+      </c>
+      <c r="H109" t="s">
+        <v>196</v>
+      </c>
+      <c r="I109" t="s">
+        <v>247</v>
+      </c>
+      <c r="J109" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A110" t="s">
+        <v>213</v>
+      </c>
+      <c r="B110" t="s">
+        <v>223</v>
+      </c>
+      <c r="C110" t="s">
+        <v>243</v>
+      </c>
+      <c r="D110" t="s">
+        <v>210</v>
+      </c>
+      <c r="E110">
+        <v>850</v>
+      </c>
+      <c r="F110" t="s">
+        <v>202</v>
+      </c>
+      <c r="G110" t="s">
+        <v>191</v>
+      </c>
+      <c r="H110" t="s">
+        <v>196</v>
+      </c>
+      <c r="I110" t="s">
+        <v>246</v>
+      </c>
+      <c r="J110" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A111" t="s">
+        <v>213</v>
+      </c>
+      <c r="B111" t="s">
+        <v>224</v>
+      </c>
+      <c r="C111" t="s">
+        <v>244</v>
+      </c>
+      <c r="D111" t="s">
+        <v>210</v>
+      </c>
+      <c r="E111">
+        <v>850</v>
+      </c>
+      <c r="F111" t="s">
+        <v>195</v>
+      </c>
+      <c r="G111" t="s">
+        <v>191</v>
+      </c>
+      <c r="H111" t="s">
+        <v>196</v>
+      </c>
+      <c r="I111" t="s">
+        <v>245</v>
+      </c>
+      <c r="J111" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A112" t="s">
+        <v>213</v>
+      </c>
+      <c r="B112" t="s">
+        <v>225</v>
+      </c>
+      <c r="C112" t="s">
+        <v>248</v>
+      </c>
+      <c r="D112" t="s">
+        <v>210</v>
+      </c>
+      <c r="E112">
+        <v>850</v>
+      </c>
+      <c r="F112" t="s">
+        <v>203</v>
+      </c>
+      <c r="G112" t="s">
+        <v>191</v>
+      </c>
+      <c r="H112" t="s">
+        <v>196</v>
+      </c>
+      <c r="I112" t="s">
+        <v>249</v>
+      </c>
+      <c r="J112" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A113" t="s">
+        <v>213</v>
+      </c>
+      <c r="B113" t="s">
+        <v>226</v>
+      </c>
+      <c r="C113" t="s">
+        <v>250</v>
+      </c>
+      <c r="D113" t="s">
+        <v>210</v>
+      </c>
+      <c r="E113">
+        <v>400</v>
+      </c>
+      <c r="F113" t="s">
+        <v>256</v>
+      </c>
+      <c r="G113" t="s">
+        <v>193</v>
+      </c>
+      <c r="H113" t="s">
+        <v>196</v>
+      </c>
+      <c r="I113" t="s">
+        <v>251</v>
+      </c>
+      <c r="J113" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A114" t="s">
+        <v>213</v>
+      </c>
+      <c r="B114" t="s">
+        <v>227</v>
+      </c>
+      <c r="C114" t="s">
+        <v>252</v>
+      </c>
+      <c r="D114" t="s">
+        <v>210</v>
+      </c>
+      <c r="E114">
+        <v>850</v>
+      </c>
+      <c r="F114" t="s">
+        <v>195</v>
+      </c>
+      <c r="G114" t="s">
+        <v>191</v>
+      </c>
+      <c r="H114" t="s">
+        <v>196</v>
+      </c>
+      <c r="I114" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A115" t="s">
+        <v>213</v>
+      </c>
+      <c r="B115" t="s">
+        <v>228</v>
+      </c>
+      <c r="C115" t="s">
+        <v>254</v>
+      </c>
+      <c r="D115" t="s">
+        <v>210</v>
+      </c>
+      <c r="E115">
+        <v>900</v>
+      </c>
+      <c r="F115" t="s">
+        <v>194</v>
+      </c>
+      <c r="G115" t="s">
+        <v>191</v>
+      </c>
+      <c r="H115" t="s">
+        <v>197</v>
+      </c>
+      <c r="I115" t="s">
+        <v>253</v>
+      </c>
+      <c r="J115" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A116" t="s">
+        <v>213</v>
+      </c>
+      <c r="B116" t="s">
+        <v>229</v>
+      </c>
+      <c r="C116" t="s">
+        <v>255</v>
+      </c>
+      <c r="D116" t="s">
+        <v>210</v>
+      </c>
+      <c r="E116">
+        <v>350</v>
+      </c>
+      <c r="F116" t="s">
+        <v>194</v>
+      </c>
+      <c r="G116" t="s">
+        <v>193</v>
+      </c>
+      <c r="H116" t="s">
+        <v>197</v>
+      </c>
+      <c r="I116" t="s">
+        <v>253</v>
+      </c>
+      <c r="J116" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A117" t="s">
+        <v>213</v>
+      </c>
+      <c r="B117" t="s">
+        <v>179</v>
+      </c>
+      <c r="C117" t="s">
+        <v>187</v>
+      </c>
+      <c r="D117" t="s">
+        <v>209</v>
+      </c>
+      <c r="E117">
+        <v>1450</v>
+      </c>
+      <c r="F117" t="s">
+        <v>194</v>
+      </c>
+      <c r="G117" t="s">
+        <v>191</v>
+      </c>
+      <c r="H117" t="s">
+        <v>196</v>
+      </c>
+      <c r="I117" t="s">
         <v>183</v>
       </c>
-      <c r="C108" t="s">
+      <c r="J117" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A118" t="s">
+        <v>213</v>
+      </c>
+      <c r="B118" t="s">
+        <v>180</v>
+      </c>
+      <c r="C118" t="s">
+        <v>188</v>
+      </c>
+      <c r="D118" t="s">
+        <v>209</v>
+      </c>
+      <c r="E118">
+        <v>650</v>
+      </c>
+      <c r="F118" t="s">
+        <v>194</v>
+      </c>
+      <c r="G118" t="s">
+        <v>193</v>
+      </c>
+      <c r="H118" t="s">
+        <v>196</v>
+      </c>
+      <c r="I118" t="s">
+        <v>183</v>
+      </c>
+      <c r="J118" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A119" t="s">
+        <v>213</v>
+      </c>
+      <c r="B119" t="s">
+        <v>289</v>
+      </c>
+      <c r="C119" t="s">
+        <v>296</v>
+      </c>
+      <c r="D119" t="s">
+        <v>209</v>
+      </c>
+      <c r="E119">
+        <v>800</v>
+      </c>
+      <c r="F119" t="s">
+        <v>194</v>
+      </c>
+      <c r="G119" t="s">
+        <v>91</v>
+      </c>
+      <c r="H119" t="s">
+        <v>197</v>
+      </c>
+      <c r="I119" t="s">
+        <v>301</v>
+      </c>
+      <c r="J119" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A120" t="s">
+        <v>213</v>
+      </c>
+      <c r="B120" t="s">
+        <v>290</v>
+      </c>
+      <c r="C120" t="s">
+        <v>295</v>
+      </c>
+      <c r="D120" t="s">
+        <v>209</v>
+      </c>
+      <c r="E120">
+        <v>650</v>
+      </c>
+      <c r="F120" t="s">
+        <v>194</v>
+      </c>
+      <c r="G120" t="s">
+        <v>204</v>
+      </c>
+      <c r="H120" t="s">
+        <v>197</v>
+      </c>
+      <c r="I120" t="s">
+        <v>301</v>
+      </c>
+      <c r="J120" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A121" t="s">
+        <v>213</v>
+      </c>
+      <c r="B121" t="s">
+        <v>291</v>
+      </c>
+      <c r="C121" t="s">
+        <v>297</v>
+      </c>
+      <c r="D121" t="s">
+        <v>209</v>
+      </c>
+      <c r="E121">
+        <v>650</v>
+      </c>
+      <c r="F121" t="s">
+        <v>194</v>
+      </c>
+      <c r="G121" t="s">
+        <v>193</v>
+      </c>
+      <c r="H121" t="s">
+        <v>197</v>
+      </c>
+      <c r="I121" t="s">
+        <v>301</v>
+      </c>
+      <c r="J121" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A122" t="s">
+        <v>213</v>
+      </c>
+      <c r="B122" t="s">
+        <v>292</v>
+      </c>
+      <c r="C122" t="s">
+        <v>298</v>
+      </c>
+      <c r="D122" t="s">
+        <v>209</v>
+      </c>
+      <c r="E122">
+        <v>650</v>
+      </c>
+      <c r="F122" t="s">
+        <v>194</v>
+      </c>
+      <c r="G122" t="s">
+        <v>91</v>
+      </c>
+      <c r="H122" t="s">
+        <v>200</v>
+      </c>
+      <c r="I122" t="s">
+        <v>301</v>
+      </c>
+      <c r="J122" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A123" t="s">
+        <v>213</v>
+      </c>
+      <c r="B123" t="s">
+        <v>293</v>
+      </c>
+      <c r="C123" t="s">
+        <v>299</v>
+      </c>
+      <c r="D123" t="s">
+        <v>209</v>
+      </c>
+      <c r="E123">
+        <v>650</v>
+      </c>
+      <c r="F123" t="s">
+        <v>194</v>
+      </c>
+      <c r="G123" t="s">
+        <v>204</v>
+      </c>
+      <c r="H123" t="s">
+        <v>200</v>
+      </c>
+      <c r="I123" t="s">
+        <v>301</v>
+      </c>
+      <c r="J123" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A124" t="s">
+        <v>213</v>
+      </c>
+      <c r="B124" t="s">
+        <v>294</v>
+      </c>
+      <c r="C124" t="s">
+        <v>300</v>
+      </c>
+      <c r="D124" t="s">
+        <v>209</v>
+      </c>
+      <c r="E124">
+        <v>800</v>
+      </c>
+      <c r="F124" t="s">
+        <v>194</v>
+      </c>
+      <c r="G124" t="s">
+        <v>193</v>
+      </c>
+      <c r="H124" t="s">
+        <v>200</v>
+      </c>
+      <c r="I124" t="s">
+        <v>301</v>
+      </c>
+      <c r="J124" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A125" t="s">
+        <v>213</v>
+      </c>
+      <c r="B125" t="s">
+        <v>181</v>
+      </c>
+      <c r="C125" t="s">
+        <v>189</v>
+      </c>
+      <c r="D125" t="s">
+        <v>210</v>
+      </c>
+      <c r="E125">
+        <v>850</v>
+      </c>
+      <c r="F125" t="s">
+        <v>194</v>
+      </c>
+      <c r="G125" t="s">
         <v>191</v>
       </c>
-      <c r="D108" t="s">
-        <v>211</v>
-      </c>
-      <c r="E108">
+      <c r="H125" t="s">
+        <v>196</v>
+      </c>
+      <c r="I125" t="s">
+        <v>184</v>
+      </c>
+      <c r="J125" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A126" t="s">
+        <v>213</v>
+      </c>
+      <c r="B126" t="s">
+        <v>182</v>
+      </c>
+      <c r="C126" t="s">
+        <v>190</v>
+      </c>
+      <c r="D126" t="s">
+        <v>210</v>
+      </c>
+      <c r="E126">
         <v>400</v>
       </c>
-      <c r="F108" t="s">
-        <v>195</v>
-      </c>
-      <c r="G108" t="s">
-        <v>194</v>
-      </c>
-      <c r="H108" t="s">
-        <v>197</v>
-      </c>
-      <c r="I108" t="s">
-        <v>185</v>
-      </c>
-      <c r="J108" t="s">
-        <v>285</v>
+      <c r="F126" t="s">
+        <v>194</v>
+      </c>
+      <c r="G126" t="s">
+        <v>193</v>
+      </c>
+      <c r="H126" t="s">
+        <v>196</v>
+      </c>
+      <c r="I126" t="s">
+        <v>184</v>
+      </c>
+      <c r="J126" t="s">
+        <v>284</v>
       </c>
     </row>
   </sheetData>

--- a/data/carddata.xlsx
+++ b/data/carddata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/41daa6e63c067b49/ドキュメント/GitHub/aikatsu-encore/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="293" documentId="8_{E3202D65-6DB6-41BF-AB49-900941BE025D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{645F5CF7-8266-4A2F-9243-CF71511D916D}"/>
+  <xr:revisionPtr revIDLastSave="310" documentId="8_{E3202D65-6DB6-41BF-AB49-900941BE025D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3A8D8CF-784A-40E5-8124-9B77CDB4FD14}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{23D23E19-BA23-4316-91CC-981E46D7F5F5}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1020" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="319">
   <si>
     <t>カード番号</t>
     <rPh sb="3" eb="5">
@@ -1310,6 +1310,14 @@
   </si>
   <si>
     <t>E1-50★</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>オーロラキス★</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>天の川コズミック★</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1387,10 +1395,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1714,14 +1718,7 @@
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="21.25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="47.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="32.625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.25" customWidth="1"/>
-    <col min="9" max="9" width="73.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="9" width="10.25" customWidth="1"/>
     <col min="10" max="10" width="23.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1899,7 +1896,7 @@
         <v>197</v>
       </c>
       <c r="J6" t="s">
-        <v>258</v>
+        <v>317</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.4">
@@ -1928,7 +1925,7 @@
         <v>197</v>
       </c>
       <c r="J7" t="s">
-        <v>258</v>
+        <v>317</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.4">
@@ -1957,7 +1954,7 @@
         <v>197</v>
       </c>
       <c r="J8" t="s">
-        <v>258</v>
+        <v>317</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.4">
@@ -1986,7 +1983,7 @@
         <v>197</v>
       </c>
       <c r="J9" t="s">
-        <v>258</v>
+        <v>317</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.4">
@@ -3008,6 +3005,9 @@
       <c r="H45" t="s">
         <v>198</v>
       </c>
+      <c r="J45" t="s">
+        <v>318</v>
+      </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
@@ -3034,6 +3034,9 @@
       <c r="H46" t="s">
         <v>198</v>
       </c>
+      <c r="J46" t="s">
+        <v>318</v>
+      </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
@@ -3060,6 +3063,9 @@
       <c r="H47" t="s">
         <v>198</v>
       </c>
+      <c r="J47" t="s">
+        <v>318</v>
+      </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
@@ -3085,6 +3091,9 @@
       </c>
       <c r="H48" t="s">
         <v>198</v>
+      </c>
+      <c r="J48" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.4">
